--- a/WB1.xlsx
+++ b/WB1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pwkut\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2043010E-2ACE-47B4-A6C2-593A1C495393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3565DC6-5C89-4E41-94AB-A8173B02E1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{93C356B9-D67D-486D-B38F-7CF05C69DA79}"/>
   </bookViews>
@@ -44,10 +44,10 @@
     <t>Column2</t>
   </si>
   <si>
-    <t>Column3</t>
+    <t>Column4</t>
   </si>
   <si>
-    <t>Column4</t>
+    <t>HUHUZ</t>
   </si>
 </sst>
 </file>
@@ -118,9 +118,9 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{A8641A11-F8E7-478B-9616-0D86DB04E548}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{80915A65-D5A5-4DD8-A385-D6CECE93AA5F}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{F9AB81DF-688B-4CE9-B0CD-5D67F73AEE51}" name="Column3"/>
+    <tableColumn id="3" xr3:uid="{F9AB81DF-688B-4CE9-B0CD-5D67F73AEE51}" name="HUHUZ"/>
     <tableColumn id="4" xr3:uid="{8BEB6E93-0158-492D-B3A5-C2CF06436F1B}" name="Column4" dataDxfId="0">
-      <calculatedColumnFormula>Table1[[#This Row],[Column1]]-Table1[[#This Row],[Column2]]</calculatedColumnFormula>
+      <calculatedColumnFormula>Table1[[#This Row],[Column1]]+Table1[[#This Row],[Column2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -458,15 +458,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D2">
-        <f>Table1[[#This Row],[Column1]]-Table1[[#This Row],[Column2]]</f>
+        <f>Table1[[#This Row],[Column1]]+Table1[[#This Row],[Column2]]</f>
         <v>0</v>
       </c>
     </row>
@@ -475,22 +475,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <f>Table1[[#This Row],[Column1]]-Table1[[#This Row],[Column2]]</f>
-        <v>-1</v>
+        <f>Table1[[#This Row],[Column1]]+Table1[[#This Row],[Column2]]</f>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D4">
-        <f>Table1[[#This Row],[Column1]]-Table1[[#This Row],[Column2]]</f>
+        <f>Table1[[#This Row],[Column1]]+Table1[[#This Row],[Column2]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>5</v>
+      </c>
       <c r="D5">
-        <f>Table1[[#This Row],[Column1]]-Table1[[#This Row],[Column2]]</f>
+        <f>Table1[[#This Row],[Column1]]+Table1[[#This Row],[Column2]]</f>
         <v>0</v>
       </c>
     </row>
